--- a/MainTop/05.08.2026 Имена Срочно/поставка.xlsx
+++ b/MainTop/05.08.2026 Имена Срочно/поставка.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\05.08.2026 Имена Срочно\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF1D5446-66A8-4A11-B56F-9EF23DF374D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C842AF88-12E9-432A-9C0B-3C50145E456B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A4649BDC-C14A-4A1F-9B1A-E430618FDFB8}"/>
   </bookViews>
